--- a/grupos/3ALCV - Estadisticos 20231.xlsx
+++ b/grupos/3ALCV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="178">
   <si>
     <t>Materia</t>
   </si>
@@ -4043,13 +4043,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>54</v>
@@ -4058,22 +4058,25 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4090,45 +4093,54 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="P2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -4145,17 +4157,17 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
         <v>95.8</v>
       </c>
-      <c r="I4">
-        <v>100</v>
-      </c>
       <c r="J4">
         <v>100</v>
       </c>
@@ -4163,22 +4175,31 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
         <v>95.8</v>
       </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
       <c r="P4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -4195,7 +4216,7 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -4213,7 +4234,7 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -4227,8 +4248,17 @@
       <c r="P5">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -4245,7 +4275,7 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -4263,7 +4293,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -4277,8 +4307,17 @@
       <c r="P6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -4295,17 +4334,17 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
         <v>95.8</v>
       </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
       <c r="J7">
         <v>100</v>
       </c>
@@ -4313,22 +4352,31 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
         <v>95.8</v>
       </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
       <c r="P7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -4345,7 +4393,7 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -4363,7 +4411,7 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -4377,8 +4425,17 @@
       <c r="P8">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -4395,17 +4452,17 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
       <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
         <v>95.8</v>
       </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
       <c r="J9">
         <v>100</v>
       </c>
@@ -4413,22 +4470,31 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
         <v>95.8</v>
       </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
       <c r="P9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -4445,7 +4511,7 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -4463,7 +4529,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -4477,8 +4543,17 @@
       <c r="P10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -4495,40 +4570,49 @@
         <v>40</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>80</v>
       </c>
-      <c r="G11">
-        <v>100</v>
-      </c>
       <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11">
         <v>12.5</v>
-      </c>
-      <c r="I11">
-        <v>40</v>
       </c>
       <c r="J11">
         <v>40</v>
       </c>
       <c r="K11">
+        <v>40</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>80</v>
       </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
-      <c r="M11">
+      <c r="N11">
+        <v>100</v>
+      </c>
+      <c r="O11">
         <v>12.5</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>40</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>40</v>
       </c>
-      <c r="P11">
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -4545,7 +4629,7 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -4563,7 +4647,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -4577,8 +4661,17 @@
       <c r="P12">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -4595,40 +4688,49 @@
         <v>100</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>85</v>
       </c>
-      <c r="G13">
-        <v>100</v>
-      </c>
       <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
         <v>95.8</v>
       </c>
-      <c r="I13">
-        <v>100</v>
-      </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>85</v>
       </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
-      <c r="M13">
+      <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
         <v>95.8</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
-        <v>100</v>
-      </c>
       <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -4645,40 +4747,49 @@
         <v>100</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>85</v>
       </c>
-      <c r="G14">
-        <v>100</v>
-      </c>
       <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
         <v>95.8</v>
       </c>
-      <c r="I14">
-        <v>100</v>
-      </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>85</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
-      <c r="M14">
+      <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
         <v>95.8</v>
       </c>
-      <c r="N14">
-        <v>100</v>
-      </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
       <c r="P14">
+        <v>100</v>
+      </c>
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -4695,40 +4806,49 @@
         <v>100</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>75</v>
       </c>
-      <c r="G15">
-        <v>100</v>
-      </c>
       <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15">
         <v>95.8</v>
       </c>
-      <c r="I15">
-        <v>100</v>
-      </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>75</v>
       </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
-      <c r="M15">
+      <c r="N15">
+        <v>100</v>
+      </c>
+      <c r="O15">
         <v>95.8</v>
       </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15">
-        <v>100</v>
-      </c>
       <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -4745,17 +4865,17 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>100</v>
       </c>
       <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
         <v>95.8</v>
       </c>
-      <c r="I16">
-        <v>100</v>
-      </c>
       <c r="J16">
         <v>100</v>
       </c>
@@ -4763,22 +4883,31 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16">
+        <v>100</v>
+      </c>
+      <c r="O16">
         <v>95.8</v>
       </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
       <c r="P16">
         <v>100</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -4795,7 +4924,7 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -4813,7 +4942,7 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -4827,8 +4956,17 @@
       <c r="P17">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -4845,7 +4983,7 @@
         <v>100</v>
       </c>
       <c r="F18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -4863,7 +5001,7 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -4877,8 +5015,17 @@
       <c r="P18">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -4895,7 +5042,7 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -4913,7 +5060,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -4927,8 +5074,17 @@
       <c r="P19">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -4945,7 +5101,7 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -4963,7 +5119,7 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -4977,8 +5133,17 @@
       <c r="P20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -4995,7 +5160,7 @@
         <v>100</v>
       </c>
       <c r="F21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -5013,7 +5178,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -5027,8 +5192,17 @@
       <c r="P21">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -5045,40 +5219,49 @@
         <v>100</v>
       </c>
       <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
         <v>90</v>
       </c>
-      <c r="G22">
-        <v>100</v>
-      </c>
       <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22">
         <v>95.8</v>
       </c>
-      <c r="I22">
-        <v>100</v>
-      </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>90</v>
       </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
-      <c r="M22">
+      <c r="N22">
+        <v>100</v>
+      </c>
+      <c r="O22">
         <v>95.8</v>
       </c>
-      <c r="N22">
-        <v>100</v>
-      </c>
-      <c r="O22">
-        <v>100</v>
-      </c>
       <c r="P22">
+        <v>100</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:19">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -5095,11 +5278,11 @@
         <v>100</v>
       </c>
       <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
         <v>90</v>
       </c>
-      <c r="G23">
-        <v>100</v>
-      </c>
       <c r="H23">
         <v>100</v>
       </c>
@@ -5110,14 +5293,14 @@
         <v>100</v>
       </c>
       <c r="K23">
+        <v>100</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>90</v>
       </c>
-      <c r="L23">
-        <v>100</v>
-      </c>
-      <c r="M23">
-        <v>100</v>
-      </c>
       <c r="N23">
         <v>100</v>
       </c>
@@ -5125,10 +5308,19 @@
         <v>100</v>
       </c>
       <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -5145,40 +5337,49 @@
         <v>100</v>
       </c>
       <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
         <v>75</v>
       </c>
-      <c r="G24">
-        <v>100</v>
-      </c>
       <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
         <v>95.8</v>
       </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>75</v>
       </c>
-      <c r="L24">
-        <v>100</v>
-      </c>
-      <c r="M24">
+      <c r="N24">
+        <v>100</v>
+      </c>
+      <c r="O24">
         <v>95.8</v>
       </c>
-      <c r="N24">
-        <v>100</v>
-      </c>
-      <c r="O24">
-        <v>100</v>
-      </c>
       <c r="P24">
+        <v>100</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -5195,40 +5396,49 @@
         <v>100</v>
       </c>
       <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <v>95</v>
       </c>
-      <c r="G25">
-        <v>100</v>
-      </c>
       <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
         <v>95.8</v>
       </c>
-      <c r="I25">
-        <v>100</v>
-      </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>95</v>
       </c>
-      <c r="L25">
-        <v>100</v>
-      </c>
-      <c r="M25">
+      <c r="N25">
+        <v>100</v>
+      </c>
+      <c r="O25">
         <v>95.8</v>
       </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25">
-        <v>100</v>
-      </c>
       <c r="P25">
+        <v>100</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -5238,20 +5448,20 @@
       <c r="E26">
         <v>100</v>
       </c>
-      <c r="I26">
-        <v>100</v>
-      </c>
       <c r="J26">
         <v>100</v>
       </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
-      <c r="O26">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="P26">
+        <v>100</v>
+      </c>
+      <c r="Q26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -5268,11 +5478,11 @@
         <v>100</v>
       </c>
       <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
         <v>90</v>
       </c>
-      <c r="G27">
-        <v>100</v>
-      </c>
       <c r="H27">
         <v>100</v>
       </c>
@@ -5283,14 +5493,14 @@
         <v>100</v>
       </c>
       <c r="K27">
+        <v>100</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>90</v>
       </c>
-      <c r="L27">
-        <v>100</v>
-      </c>
-      <c r="M27">
-        <v>100</v>
-      </c>
       <c r="N27">
         <v>100</v>
       </c>
@@ -5298,10 +5508,19 @@
         <v>100</v>
       </c>
       <c r="P27">
+        <v>100</v>
+      </c>
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -5318,11 +5537,11 @@
         <v>100</v>
       </c>
       <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
         <v>85</v>
       </c>
-      <c r="G28">
-        <v>100</v>
-      </c>
       <c r="H28">
         <v>100</v>
       </c>
@@ -5333,14 +5552,14 @@
         <v>100</v>
       </c>
       <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>85</v>
       </c>
-      <c r="L28">
-        <v>100</v>
-      </c>
-      <c r="M28">
-        <v>100</v>
-      </c>
       <c r="N28">
         <v>100</v>
       </c>
@@ -5348,10 +5567,19 @@
         <v>100</v>
       </c>
       <c r="P28">
+        <v>100</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:19">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -5368,7 +5596,7 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>100</v>
@@ -5386,7 +5614,7 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -5400,8 +5628,17 @@
       <c r="P29">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:16">
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -5418,7 +5655,7 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G30">
         <v>100</v>
@@ -5436,7 +5673,7 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -5450,8 +5687,17 @@
       <c r="P30">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
@@ -5468,40 +5714,49 @@
         <v>100</v>
       </c>
       <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
         <v>80</v>
       </c>
-      <c r="G31">
-        <v>100</v>
-      </c>
       <c r="H31">
+        <v>100</v>
+      </c>
+      <c r="I31">
         <v>95.8</v>
       </c>
-      <c r="I31">
-        <v>100</v>
-      </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
         <v>80</v>
       </c>
-      <c r="L31">
-        <v>100</v>
-      </c>
-      <c r="M31">
+      <c r="N31">
+        <v>100</v>
+      </c>
+      <c r="O31">
         <v>95.8</v>
       </c>
-      <c r="N31">
-        <v>100</v>
-      </c>
-      <c r="O31">
-        <v>100</v>
-      </c>
       <c r="P31">
+        <v>100</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:19">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -5518,17 +5773,17 @@
         <v>100</v>
       </c>
       <c r="F32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32">
         <v>100</v>
       </c>
       <c r="H32">
+        <v>100</v>
+      </c>
+      <c r="I32">
         <v>95.8</v>
       </c>
-      <c r="I32">
-        <v>100</v>
-      </c>
       <c r="J32">
         <v>100</v>
       </c>
@@ -5536,22 +5791,31 @@
         <v>100</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M32">
+        <v>100</v>
+      </c>
+      <c r="N32">
+        <v>100</v>
+      </c>
+      <c r="O32">
         <v>95.8</v>
       </c>
-      <c r="N32">
-        <v>100</v>
-      </c>
-      <c r="O32">
-        <v>100</v>
-      </c>
       <c r="P32">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -5561,20 +5825,20 @@
       <c r="E33">
         <v>100</v>
       </c>
-      <c r="I33">
-        <v>100</v>
-      </c>
       <c r="J33">
         <v>100</v>
       </c>
-      <c r="N33">
-        <v>100</v>
-      </c>
-      <c r="O33">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
+      <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="P33">
+        <v>100</v>
+      </c>
+      <c r="Q33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" s="1" t="s">
         <v>42</v>
       </c>
@@ -5591,17 +5855,17 @@
         <v>100</v>
       </c>
       <c r="F34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G34">
         <v>100</v>
       </c>
       <c r="H34">
+        <v>100</v>
+      </c>
+      <c r="I34">
         <v>95.8</v>
       </c>
-      <c r="I34">
-        <v>100</v>
-      </c>
       <c r="J34">
         <v>100</v>
       </c>
@@ -5609,22 +5873,31 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M34">
+        <v>100</v>
+      </c>
+      <c r="N34">
+        <v>100</v>
+      </c>
+      <c r="O34">
         <v>95.8</v>
       </c>
-      <c r="N34">
-        <v>100</v>
-      </c>
-      <c r="O34">
-        <v>100</v>
-      </c>
       <c r="P34">
         <v>100</v>
       </c>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="Q34">
+        <v>100</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" s="1" t="s">
         <v>43</v>
       </c>
@@ -5641,17 +5914,17 @@
         <v>100</v>
       </c>
       <c r="F35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G35">
         <v>100</v>
       </c>
       <c r="H35">
+        <v>100</v>
+      </c>
+      <c r="I35">
         <v>95.8</v>
       </c>
-      <c r="I35">
-        <v>100</v>
-      </c>
       <c r="J35">
         <v>100</v>
       </c>
@@ -5659,22 +5932,31 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M35">
+        <v>100</v>
+      </c>
+      <c r="N35">
+        <v>100</v>
+      </c>
+      <c r="O35">
         <v>95.8</v>
       </c>
-      <c r="N35">
-        <v>100</v>
-      </c>
-      <c r="O35">
-        <v>100</v>
-      </c>
       <c r="P35">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="1:16">
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36" s="1" t="s">
         <v>44</v>
       </c>
@@ -5691,7 +5973,7 @@
         <v>100</v>
       </c>
       <c r="F36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <v>100</v>
@@ -5709,7 +5991,7 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -5723,8 +6005,17 @@
       <c r="P36">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="1:16">
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37" s="1" t="s">
         <v>45</v>
       </c>
@@ -5741,11 +6032,11 @@
         <v>100</v>
       </c>
       <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
         <v>95</v>
       </c>
-      <c r="G37">
-        <v>100</v>
-      </c>
       <c r="H37">
         <v>100</v>
       </c>
@@ -5756,14 +6047,14 @@
         <v>100</v>
       </c>
       <c r="K37">
+        <v>100</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
         <v>95</v>
       </c>
-      <c r="L37">
-        <v>100</v>
-      </c>
-      <c r="M37">
-        <v>100</v>
-      </c>
       <c r="N37">
         <v>100</v>
       </c>
@@ -5771,10 +6062,19 @@
         <v>100</v>
       </c>
       <c r="P37">
+        <v>100</v>
+      </c>
+      <c r="Q37">
+        <v>100</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:19">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
@@ -5784,20 +6084,20 @@
       <c r="E38">
         <v>100</v>
       </c>
-      <c r="I38">
-        <v>100</v>
-      </c>
       <c r="J38">
         <v>100</v>
       </c>
-      <c r="N38">
-        <v>100</v>
-      </c>
-      <c r="O38">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16">
+      <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="P38">
+        <v>100</v>
+      </c>
+      <c r="Q38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
       <c r="A39" s="1" t="s">
         <v>47</v>
       </c>
@@ -5814,40 +6114,49 @@
         <v>100</v>
       </c>
       <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
         <v>75</v>
       </c>
-      <c r="G39">
-        <v>100</v>
-      </c>
       <c r="H39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J39">
         <v>100</v>
       </c>
       <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
         <v>75</v>
       </c>
-      <c r="L39">
-        <v>100</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
       <c r="N39">
         <v>100</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P39">
+        <v>100</v>
+      </c>
+      <c r="Q39">
+        <v>100</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:19">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
@@ -5864,17 +6173,17 @@
         <v>100</v>
       </c>
       <c r="F40">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G40">
         <v>100</v>
       </c>
       <c r="H40">
+        <v>100</v>
+      </c>
+      <c r="I40">
         <v>95.8</v>
       </c>
-      <c r="I40">
-        <v>100</v>
-      </c>
       <c r="J40">
         <v>100</v>
       </c>
@@ -5882,22 +6191,31 @@
         <v>100</v>
       </c>
       <c r="L40">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M40">
+        <v>100</v>
+      </c>
+      <c r="N40">
+        <v>100</v>
+      </c>
+      <c r="O40">
         <v>95.8</v>
       </c>
-      <c r="N40">
-        <v>100</v>
-      </c>
-      <c r="O40">
-        <v>100</v>
-      </c>
       <c r="P40">
         <v>100</v>
       </c>
-    </row>
-    <row r="41" spans="1:16">
+      <c r="Q40">
+        <v>100</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41" s="1" t="s">
         <v>49</v>
       </c>
@@ -5907,20 +6225,20 @@
       <c r="E41">
         <v>100</v>
       </c>
-      <c r="I41">
-        <v>100</v>
-      </c>
       <c r="J41">
         <v>100</v>
       </c>
-      <c r="N41">
-        <v>100</v>
-      </c>
-      <c r="O41">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16">
+      <c r="K41">
+        <v>100</v>
+      </c>
+      <c r="P41">
+        <v>100</v>
+      </c>
+      <c r="Q41">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
       <c r="A42" s="1" t="s">
         <v>50</v>
       </c>
@@ -5937,7 +6255,7 @@
         <v>100</v>
       </c>
       <c r="F42">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -5955,7 +6273,7 @@
         <v>100</v>
       </c>
       <c r="L42">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M42">
         <v>100</v>
@@ -5969,8 +6287,17 @@
       <c r="P42">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="1:16">
+      <c r="Q42">
+        <v>100</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19">
       <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
@@ -5987,40 +6314,49 @@
         <v>100</v>
       </c>
       <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
         <v>90</v>
       </c>
-      <c r="G43">
-        <v>100</v>
-      </c>
       <c r="H43">
+        <v>100</v>
+      </c>
+      <c r="I43">
         <v>95.8</v>
       </c>
-      <c r="I43">
-        <v>100</v>
-      </c>
       <c r="J43">
         <v>100</v>
       </c>
       <c r="K43">
+        <v>100</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
         <v>90</v>
       </c>
-      <c r="L43">
-        <v>100</v>
-      </c>
-      <c r="M43">
+      <c r="N43">
+        <v>100</v>
+      </c>
+      <c r="O43">
         <v>95.8</v>
       </c>
-      <c r="N43">
-        <v>100</v>
-      </c>
-      <c r="O43">
-        <v>100</v>
-      </c>
       <c r="P43">
+        <v>100</v>
+      </c>
+      <c r="Q43">
+        <v>100</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:19">
       <c r="A44" s="1" t="s">
         <v>52</v>
       </c>
@@ -6030,20 +6366,20 @@
       <c r="E44">
         <v>100</v>
       </c>
-      <c r="I44">
-        <v>100</v>
-      </c>
       <c r="J44">
         <v>100</v>
       </c>
-      <c r="N44">
-        <v>100</v>
-      </c>
-      <c r="O44">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="K44">
+        <v>100</v>
+      </c>
+      <c r="P44">
+        <v>100</v>
+      </c>
+      <c r="Q44">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19">
       <c r="A45" s="1" t="s">
         <v>53</v>
       </c>
@@ -6060,11 +6396,11 @@
         <v>100</v>
       </c>
       <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
         <v>95</v>
       </c>
-      <c r="G45">
-        <v>100</v>
-      </c>
       <c r="H45">
         <v>100</v>
       </c>
@@ -6075,14 +6411,14 @@
         <v>100</v>
       </c>
       <c r="K45">
+        <v>100</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
         <v>95</v>
       </c>
-      <c r="L45">
-        <v>100</v>
-      </c>
-      <c r="M45">
-        <v>100</v>
-      </c>
       <c r="N45">
         <v>100</v>
       </c>
@@ -6090,14 +6426,23 @@
         <v>100</v>
       </c>
       <c r="P45">
+        <v>100</v>
+      </c>
+      <c r="Q45">
+        <v>100</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
         <v>95</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/3ALCV - Estadisticos 20231.xlsx
+++ b/grupos/3ALCV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -119,9 +119,6 @@
     <t>LLANOS SANTIAGO SERGIO</t>
   </si>
   <si>
-    <t>LOPEZ CIRUELO LUISA MARIA</t>
-  </si>
-  <si>
     <t>MALDONADO SERRANO IVONNE SHERLINE</t>
   </si>
   <si>
@@ -218,21 +215,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -248,310 +245,85 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>AMALIA PAULINA</t>
   </si>
   <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>GAYTAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>DE ROMAN</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZAVALA</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>APOLINAR</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>LUZ ARELY</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>AZURA</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>FERNANDA MARGARITA</t>
-  </si>
-  <si>
-    <t>ANA SHECIT</t>
-  </si>
-  <si>
-    <t>ATZIRI</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
     <t>LUZ ALONDRA</t>
   </si>
   <si>
-    <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>KARLOS ARATH</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
     <t>JARET</t>
   </si>
   <si>
-    <t>MARIA ANGELES</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
     <t>NIDIA GABRIELA</t>
   </si>
   <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>LUISA MARIA</t>
-  </si>
-  <si>
-    <t>LILIAN</t>
-  </si>
-  <si>
-    <t>JULIO ANTONIO</t>
-  </si>
-  <si>
-    <t>ATZIN LUCERO</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>ADAMARI</t>
-  </si>
-  <si>
-    <t>NOEMI DEL ROCIO</t>
-  </si>
-  <si>
-    <t>NATHALI</t>
-  </si>
-  <si>
     <t>AILYN</t>
   </si>
   <si>
-    <t>HAZEL</t>
-  </si>
-  <si>
-    <t>KAREN ARLET</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
     <t>JONATHAN</t>
   </si>
   <si>
-    <t>JUAN EMANUEL</t>
-  </si>
-  <si>
     <t>BRENDA JANELY</t>
-  </si>
-  <si>
-    <t>AXEL GAEL</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>MENA</t>
   </si>
 </sst>
 </file>
@@ -913,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1053,28 +825,28 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G4">
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1095,22 +867,22 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1130,28 +902,28 @@
         <v>9</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1181,13 +953,13 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1207,28 +979,28 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1258,13 +1030,13 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1284,28 +1056,28 @@
         <v>8</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1326,10 +1098,10 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1338,10 +1110,10 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1361,28 +1133,28 @@
         <v>8</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1406,7 +1178,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1415,10 +1187,10 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1438,28 +1210,28 @@
         <v>7</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1492,10 +1264,10 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1515,28 +1287,28 @@
         <v>8</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G10">
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1560,7 +1332,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1569,7 +1341,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1592,28 +1364,28 @@
         <v>5</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1646,7 +1418,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1669,28 +1441,28 @@
         <v>7</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1714,19 +1486,19 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1746,28 +1518,28 @@
         <v>7</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1788,7 +1560,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1800,7 +1572,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1823,28 +1595,28 @@
         <v>8</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1865,7 +1637,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -1877,7 +1649,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1900,28 +1672,28 @@
         <v>5</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1942,10 +1714,10 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -1954,7 +1726,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1977,28 +1749,28 @@
         <v>5</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2022,7 +1794,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -2031,7 +1803,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -2054,28 +1826,28 @@
         <v>8</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2099,7 +1871,7 @@
         <v>8</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2108,7 +1880,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -2131,28 +1903,28 @@
         <v>6</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G18">
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2176,19 +1948,19 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2208,28 +1980,28 @@
         <v>6</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G19">
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2250,22 +2022,22 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>10</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>6</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2285,28 +2057,28 @@
         <v>8</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2339,10 +2111,10 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2362,28 +2134,28 @@
         <v>8</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2416,7 +2188,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2439,28 +2211,28 @@
         <v>7</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2481,10 +2253,10 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -2493,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2516,28 +2288,28 @@
         <v>8</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2558,10 +2330,10 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2570,10 +2342,10 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2593,28 +2365,28 @@
         <v>6</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2635,19 +2407,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2657,47 +2429,17 @@
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>8</v>
-      </c>
-      <c r="C25">
-        <v>7</v>
-      </c>
       <c r="D25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25">
-        <v>7</v>
-      </c>
-      <c r="F25">
-        <v>-1</v>
-      </c>
-      <c r="G25">
-        <v>9</v>
-      </c>
-      <c r="H25">
-        <v>-1</v>
-      </c>
-      <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
-      </c>
-      <c r="L25">
-        <v>-1</v>
-      </c>
-      <c r="M25">
-        <v>-1</v>
-      </c>
-      <c r="N25">
-        <v>-1</v>
-      </c>
-      <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2705,45 +2447,57 @@
       <c r="Q25">
         <v>-1</v>
       </c>
-      <c r="R25">
-        <v>-1</v>
-      </c>
-      <c r="S25">
-        <v>-1</v>
-      </c>
-      <c r="T25">
-        <v>8</v>
-      </c>
-      <c r="U25">
-        <v>7</v>
-      </c>
       <c r="V25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>7</v>
-      </c>
-      <c r="X25">
-        <v>-1</v>
-      </c>
-      <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>7</v>
+      </c>
       <c r="D26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+      <c r="H26">
+        <v>8</v>
+      </c>
+      <c r="I26">
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
+        <v>7</v>
+      </c>
+      <c r="L26">
+        <v>-1</v>
+      </c>
+      <c r="M26">
+        <v>6</v>
+      </c>
+      <c r="N26">
+        <v>-1</v>
+      </c>
+      <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
@@ -2752,11 +2506,29 @@
       <c r="Q26">
         <v>-1</v>
       </c>
+      <c r="R26">
+        <v>-1</v>
+      </c>
+      <c r="S26">
+        <v>-1</v>
+      </c>
+      <c r="T26">
+        <v>7</v>
+      </c>
+      <c r="U26">
+        <v>7</v>
+      </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="X26">
+        <v>7</v>
+      </c>
+      <c r="Y26">
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2764,10 +2536,10 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -2776,28 +2548,28 @@
         <v>6</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2818,22 +2590,22 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2841,40 +2613,40 @@
         <v>36</v>
       </c>
       <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28">
+        <v>7</v>
+      </c>
+      <c r="D28">
+        <v>8</v>
+      </c>
+      <c r="E28">
+        <v>8</v>
+      </c>
+      <c r="F28">
+        <v>9</v>
+      </c>
+      <c r="G28">
         <v>10</v>
       </c>
-      <c r="C28">
-        <v>9</v>
-      </c>
-      <c r="D28">
-        <v>6</v>
-      </c>
-      <c r="E28">
-        <v>6</v>
-      </c>
-      <c r="F28">
-        <v>-1</v>
-      </c>
-      <c r="G28">
-        <v>7</v>
-      </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2895,22 +2667,22 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2918,7 +2690,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -2930,28 +2702,28 @@
         <v>8</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2972,7 +2744,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -2984,10 +2756,10 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2995,40 +2767,40 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G30">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3049,22 +2821,22 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3072,40 +2844,40 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3126,69 +2898,39 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B32">
-        <v>9</v>
-      </c>
-      <c r="C32">
-        <v>7</v>
-      </c>
       <c r="D32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>7</v>
-      </c>
-      <c r="F32">
-        <v>-1</v>
-      </c>
-      <c r="G32">
-        <v>9</v>
-      </c>
-      <c r="H32">
-        <v>-1</v>
-      </c>
-      <c r="I32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
-      </c>
-      <c r="L32">
-        <v>-1</v>
-      </c>
-      <c r="M32">
-        <v>-1</v>
-      </c>
-      <c r="N32">
-        <v>-1</v>
-      </c>
-      <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3196,45 +2938,57 @@
       <c r="Q32">
         <v>-1</v>
       </c>
-      <c r="R32">
-        <v>-1</v>
-      </c>
-      <c r="S32">
-        <v>-1</v>
-      </c>
-      <c r="T32">
-        <v>9</v>
-      </c>
-      <c r="U32">
-        <v>7</v>
-      </c>
       <c r="V32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W32">
-        <v>7</v>
-      </c>
-      <c r="X32">
-        <v>-1</v>
-      </c>
-      <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="B33">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>6</v>
+      </c>
       <c r="D33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33">
+        <v>5</v>
+      </c>
+      <c r="I33">
+        <v>5</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
+        <v>6</v>
+      </c>
+      <c r="L33">
+        <v>-1</v>
+      </c>
+      <c r="M33">
+        <v>5</v>
+      </c>
+      <c r="N33">
+        <v>-1</v>
+      </c>
+      <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
@@ -3243,11 +2997,29 @@
       <c r="Q33">
         <v>-1</v>
       </c>
+      <c r="R33">
+        <v>-1</v>
+      </c>
+      <c r="S33">
+        <v>-1</v>
+      </c>
+      <c r="T33">
+        <v>6</v>
+      </c>
+      <c r="U33">
+        <v>5</v>
+      </c>
       <c r="V33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="X33">
+        <v>5</v>
+      </c>
+      <c r="Y33">
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3255,40 +3027,40 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3315,13 +3087,13 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3332,40 +3104,40 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3386,22 +3158,22 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3409,40 +3181,40 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3463,69 +3235,39 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B37">
-        <v>9</v>
-      </c>
-      <c r="C37">
-        <v>9</v>
-      </c>
       <c r="D37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>9</v>
-      </c>
-      <c r="F37">
-        <v>-1</v>
-      </c>
-      <c r="G37">
-        <v>10</v>
-      </c>
-      <c r="H37">
-        <v>-1</v>
-      </c>
-      <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>-1</v>
-      </c>
-      <c r="L37">
-        <v>-1</v>
-      </c>
-      <c r="M37">
-        <v>-1</v>
-      </c>
-      <c r="N37">
-        <v>-1</v>
-      </c>
-      <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3533,45 +3275,57 @@
       <c r="Q37">
         <v>-1</v>
       </c>
-      <c r="R37">
-        <v>-1</v>
-      </c>
-      <c r="S37">
-        <v>-1</v>
-      </c>
-      <c r="T37">
-        <v>9</v>
-      </c>
-      <c r="U37">
-        <v>9</v>
-      </c>
       <c r="V37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W37">
-        <v>9</v>
-      </c>
-      <c r="X37">
-        <v>-1</v>
-      </c>
-      <c r="Y37">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="B38">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>5</v>
+      </c>
       <c r="D38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E38">
+        <v>8</v>
+      </c>
+      <c r="F38">
+        <v>6</v>
+      </c>
+      <c r="G38">
+        <v>6</v>
+      </c>
+      <c r="H38">
+        <v>7</v>
+      </c>
+      <c r="I38">
         <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
+        <v>7</v>
+      </c>
+      <c r="L38">
+        <v>-1</v>
+      </c>
+      <c r="M38">
+        <v>6</v>
+      </c>
+      <c r="N38">
+        <v>-1</v>
+      </c>
+      <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
@@ -3580,11 +3334,29 @@
       <c r="Q38">
         <v>-1</v>
       </c>
+      <c r="R38">
+        <v>-1</v>
+      </c>
+      <c r="S38">
+        <v>-1</v>
+      </c>
+      <c r="T38">
+        <v>7</v>
+      </c>
+      <c r="U38">
+        <v>5</v>
+      </c>
       <c r="V38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="X38">
+        <v>6</v>
+      </c>
+      <c r="Y38">
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3592,40 +3364,40 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L39">
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3646,69 +3418,39 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B40">
-        <v>7</v>
-      </c>
-      <c r="C40">
-        <v>8</v>
-      </c>
       <c r="D40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40">
-        <v>7</v>
-      </c>
-      <c r="F40">
-        <v>-1</v>
-      </c>
-      <c r="G40">
-        <v>9</v>
-      </c>
-      <c r="H40">
-        <v>-1</v>
-      </c>
-      <c r="I40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K40">
-        <v>-1</v>
-      </c>
-      <c r="L40">
-        <v>-1</v>
-      </c>
-      <c r="M40">
-        <v>-1</v>
-      </c>
-      <c r="N40">
-        <v>-1</v>
-      </c>
-      <c r="O40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -3716,45 +3458,57 @@
       <c r="Q40">
         <v>-1</v>
       </c>
-      <c r="R40">
-        <v>-1</v>
-      </c>
-      <c r="S40">
-        <v>-1</v>
-      </c>
-      <c r="T40">
-        <v>7</v>
-      </c>
-      <c r="U40">
-        <v>8</v>
-      </c>
       <c r="V40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W40">
-        <v>7</v>
-      </c>
-      <c r="X40">
-        <v>-1</v>
-      </c>
-      <c r="Y40">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="B41">
+        <v>5</v>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
       <c r="D41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E41">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41">
+        <v>8</v>
+      </c>
+      <c r="H41">
+        <v>8</v>
+      </c>
+      <c r="I41">
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K41">
+        <v>7</v>
+      </c>
+      <c r="L41">
+        <v>-1</v>
+      </c>
+      <c r="M41">
+        <v>5</v>
+      </c>
+      <c r="N41">
+        <v>-1</v>
+      </c>
+      <c r="O41">
         <v>-1</v>
       </c>
       <c r="P41">
@@ -3763,11 +3517,29 @@
       <c r="Q41">
         <v>-1</v>
       </c>
+      <c r="R41">
+        <v>-1</v>
+      </c>
+      <c r="S41">
+        <v>-1</v>
+      </c>
+      <c r="T41">
+        <v>7</v>
+      </c>
+      <c r="U41">
+        <v>6</v>
+      </c>
       <c r="V41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W41">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="X41">
+        <v>7</v>
+      </c>
+      <c r="Y41">
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3775,40 +3547,40 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L42">
         <v>-1</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -3829,69 +3601,39 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B43">
-        <v>7</v>
-      </c>
-      <c r="C43">
-        <v>5</v>
-      </c>
       <c r="D43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E43">
-        <v>6</v>
-      </c>
-      <c r="F43">
-        <v>-1</v>
-      </c>
-      <c r="G43">
-        <v>7</v>
-      </c>
-      <c r="H43">
-        <v>-1</v>
-      </c>
-      <c r="I43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>-1</v>
-      </c>
-      <c r="L43">
-        <v>-1</v>
-      </c>
-      <c r="M43">
-        <v>-1</v>
-      </c>
-      <c r="N43">
-        <v>-1</v>
-      </c>
-      <c r="O43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P43">
         <v>-1</v>
@@ -3899,28 +3641,10 @@
       <c r="Q43">
         <v>-1</v>
       </c>
-      <c r="R43">
-        <v>-1</v>
-      </c>
-      <c r="S43">
-        <v>-1</v>
-      </c>
-      <c r="T43">
-        <v>7</v>
-      </c>
-      <c r="U43">
-        <v>5</v>
-      </c>
       <c r="V43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W43">
-        <v>6</v>
-      </c>
-      <c r="X43">
-        <v>-1</v>
-      </c>
-      <c r="Y43">
         <v>7</v>
       </c>
     </row>
@@ -3928,16 +3652,46 @@
       <c r="A44" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="B44">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>7</v>
+      </c>
       <c r="D44">
         <v>7</v>
       </c>
       <c r="E44">
         <v>7</v>
       </c>
+      <c r="F44">
+        <v>6</v>
+      </c>
+      <c r="G44">
+        <v>7</v>
+      </c>
+      <c r="H44">
+        <v>6</v>
+      </c>
+      <c r="I44">
+        <v>5</v>
+      </c>
       <c r="J44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K44">
+        <v>7</v>
+      </c>
+      <c r="L44">
+        <v>-1</v>
+      </c>
+      <c r="M44">
+        <v>5</v>
+      </c>
+      <c r="N44">
+        <v>-1</v>
+      </c>
+      <c r="O44">
         <v>-1</v>
       </c>
       <c r="P44">
@@ -3946,88 +3700,29 @@
       <c r="Q44">
         <v>-1</v>
       </c>
+      <c r="R44">
+        <v>-1</v>
+      </c>
+      <c r="S44">
+        <v>-1</v>
+      </c>
+      <c r="T44">
+        <v>7</v>
+      </c>
+      <c r="U44">
+        <v>6</v>
+      </c>
       <c r="V44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W44">
         <v>7</v>
       </c>
-    </row>
-    <row r="45" spans="1:25">
-      <c r="A45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45">
-        <v>7</v>
-      </c>
-      <c r="C45">
-        <v>7</v>
-      </c>
-      <c r="D45">
-        <v>7</v>
-      </c>
-      <c r="E45">
-        <v>7</v>
-      </c>
-      <c r="F45">
-        <v>-1</v>
-      </c>
-      <c r="G45">
-        <v>7</v>
-      </c>
-      <c r="H45">
-        <v>-1</v>
-      </c>
-      <c r="I45">
-        <v>-1</v>
-      </c>
-      <c r="J45">
-        <v>-1</v>
-      </c>
-      <c r="K45">
-        <v>-1</v>
-      </c>
-      <c r="L45">
-        <v>-1</v>
-      </c>
-      <c r="M45">
-        <v>-1</v>
-      </c>
-      <c r="N45">
-        <v>-1</v>
-      </c>
-      <c r="O45">
-        <v>-1</v>
-      </c>
-      <c r="P45">
-        <v>-1</v>
-      </c>
-      <c r="Q45">
-        <v>-1</v>
-      </c>
-      <c r="R45">
-        <v>-1</v>
-      </c>
-      <c r="S45">
-        <v>-1</v>
-      </c>
-      <c r="T45">
-        <v>7</v>
-      </c>
-      <c r="U45">
-        <v>7</v>
-      </c>
-      <c r="V45">
-        <v>7</v>
-      </c>
-      <c r="W45">
-        <v>7</v>
-      </c>
-      <c r="X45">
-        <v>-1</v>
-      </c>
-      <c r="Y45">
-        <v>7</v>
+      <c r="X44">
+        <v>6</v>
+      </c>
+      <c r="Y44">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4043,7 +3738,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -4052,7 +3747,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4060,7 +3755,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -4068,7 +3763,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -4157,7 +3852,7 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -4166,7 +3861,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -4175,16 +3870,16 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -4193,10 +3888,10 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4216,7 +3911,7 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -4234,10 +3929,10 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="N5">
         <v>100</v>
@@ -4252,10 +3947,10 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4275,7 +3970,7 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -4293,10 +3988,10 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -4311,10 +4006,10 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4334,7 +4029,7 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -4343,7 +4038,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -4352,16 +4047,16 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -4370,10 +4065,10 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4393,7 +4088,7 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -4411,10 +4106,10 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="N8">
         <v>100</v>
@@ -4429,10 +4124,10 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4452,7 +4147,7 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -4461,7 +4156,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -4470,7 +4165,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -4479,7 +4174,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -4488,7 +4183,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4511,7 +4206,7 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -4529,10 +4224,10 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -4547,10 +4242,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4570,46 +4265,46 @@
         <v>40</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G11">
         <v>80</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I11">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="J11">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K11">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="M11">
-        <v>80</v>
+        <v>73.8</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O11">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="P11">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="Q11">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="S11">
-        <v>80</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4629,7 +4324,7 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -4647,10 +4342,10 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -4665,10 +4360,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4688,7 +4383,7 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>85</v>
@@ -4697,7 +4392,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -4706,16 +4401,16 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M13">
-        <v>85</v>
+        <v>76.2</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4724,10 +4419,10 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S13">
-        <v>85</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4747,7 +4442,7 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>85</v>
@@ -4756,7 +4451,7 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -4765,16 +4460,16 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4783,10 +4478,10 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4806,7 +4501,7 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>75</v>
@@ -4815,7 +4510,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4824,16 +4519,16 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M15">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4842,10 +4537,10 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S15">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4865,7 +4560,7 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -4874,7 +4569,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4883,16 +4578,16 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4901,10 +4596,10 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4924,7 +4619,7 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -4933,7 +4628,7 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -4942,16 +4637,16 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N17">
         <v>100</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4960,10 +4655,10 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4983,7 +4678,7 @@
         <v>100</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -4992,7 +4687,7 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -5001,16 +4696,16 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -5019,10 +4714,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -5042,7 +4737,7 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -5060,10 +4755,10 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -5078,10 +4773,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -5101,7 +4796,7 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -5119,10 +4814,10 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="N20">
         <v>100</v>
@@ -5137,10 +4832,10 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -5160,7 +4855,7 @@
         <v>100</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -5178,10 +4873,10 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -5196,10 +4891,10 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -5219,7 +4914,7 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G22">
         <v>90</v>
@@ -5228,7 +4923,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -5237,16 +4932,16 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="M22">
-        <v>90</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="N22">
         <v>100</v>
       </c>
       <c r="O22">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -5255,10 +4950,10 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="S22">
-        <v>90</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5278,7 +4973,7 @@
         <v>100</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>90</v>
@@ -5296,10 +4991,10 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -5314,10 +5009,10 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>90</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5337,7 +5032,7 @@
         <v>100</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G24">
         <v>75</v>
@@ -5346,7 +5041,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -5355,16 +5050,16 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="M24">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N24">
         <v>100</v>
       </c>
       <c r="O24">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5373,92 +5068,92 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="S24">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>100</v>
-      </c>
-      <c r="C25">
-        <v>95.8</v>
-      </c>
       <c r="D25">
         <v>100</v>
       </c>
       <c r="E25">
         <v>100</v>
       </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>95</v>
-      </c>
-      <c r="H25">
-        <v>100</v>
-      </c>
-      <c r="I25">
-        <v>95.8</v>
-      </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>95</v>
-      </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25">
-        <v>95.8</v>
-      </c>
       <c r="P25">
         <v>100</v>
       </c>
       <c r="Q25">
         <v>100</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="B26">
+        <v>100</v>
+      </c>
+      <c r="C26">
+        <v>100</v>
+      </c>
       <c r="D26">
         <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
       </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
+        <v>90</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>97.8</v>
+      </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
+      <c r="L26">
+        <v>50</v>
+      </c>
+      <c r="M26">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
+        <v>97.8</v>
+      </c>
       <c r="P26">
         <v>100</v>
       </c>
       <c r="Q26">
         <v>100</v>
+      </c>
+      <c r="R26">
+        <v>50</v>
+      </c>
+      <c r="S26">
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5478,10 +5173,10 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H27">
         <v>100</v>
@@ -5496,10 +5191,10 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M27">
-        <v>90</v>
+        <v>76.2</v>
       </c>
       <c r="N27">
         <v>100</v>
@@ -5514,10 +5209,10 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S27">
-        <v>90</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5537,10 +5232,10 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H28">
         <v>100</v>
@@ -5555,10 +5250,10 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M28">
-        <v>85</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -5573,10 +5268,10 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S28">
-        <v>85</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5596,7 +5291,7 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>100</v>
@@ -5605,7 +5300,7 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -5614,16 +5309,16 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="N29">
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -5632,10 +5327,10 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5646,7 +5341,7 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -5655,46 +5350,46 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H30">
         <v>100</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>73.8</v>
       </c>
       <c r="N30">
         <v>100</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P30">
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5714,16 +5409,16 @@
         <v>100</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>100</v>
       </c>
       <c r="I31">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J31">
         <v>100</v>
@@ -5732,16 +5427,16 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M31">
-        <v>80</v>
+        <v>95.2</v>
       </c>
       <c r="N31">
         <v>100</v>
       </c>
       <c r="O31">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -5750,68 +5445,32 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S31">
-        <v>80</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B32">
-        <v>100</v>
-      </c>
-      <c r="C32">
-        <v>95.8</v>
-      </c>
       <c r="D32">
         <v>100</v>
       </c>
       <c r="E32">
         <v>100</v>
       </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>100</v>
-      </c>
-      <c r="H32">
-        <v>100</v>
-      </c>
-      <c r="I32">
-        <v>95.8</v>
-      </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
         <v>100</v>
       </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>100</v>
-      </c>
-      <c r="N32">
-        <v>100</v>
-      </c>
-      <c r="O32">
-        <v>95.8</v>
-      </c>
       <c r="P32">
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>100</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
         <v>100</v>
       </c>
     </row>
@@ -5819,23 +5478,59 @@
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="B33">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>95.8</v>
+      </c>
       <c r="D33">
         <v>100</v>
       </c>
       <c r="E33">
         <v>100</v>
       </c>
+      <c r="F33">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="G33">
+        <v>100</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
+      </c>
+      <c r="I33">
+        <v>95.7</v>
+      </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
+      <c r="L33">
+        <v>44.4</v>
+      </c>
+      <c r="M33">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="N33">
+        <v>100</v>
+      </c>
+      <c r="O33">
+        <v>95.7</v>
+      </c>
       <c r="P33">
         <v>100</v>
       </c>
       <c r="Q33">
         <v>100</v>
+      </c>
+      <c r="R33">
+        <v>44.4</v>
+      </c>
+      <c r="S33">
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5855,7 +5550,7 @@
         <v>100</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>100</v>
@@ -5864,37 +5559,37 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>95.8</v>
+        <v>93.5</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M34">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N34">
         <v>100</v>
       </c>
       <c r="O34">
-        <v>95.8</v>
+        <v>93.5</v>
       </c>
       <c r="P34">
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S34">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5905,7 +5600,7 @@
         <v>100</v>
       </c>
       <c r="C35">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -5914,7 +5609,7 @@
         <v>100</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>100</v>
@@ -5923,7 +5618,7 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J35">
         <v>100</v>
@@ -5932,16 +5627,16 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="N35">
         <v>100</v>
       </c>
       <c r="O35">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -5950,10 +5645,10 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5973,16 +5668,16 @@
         <v>100</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H36">
         <v>100</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J36">
         <v>100</v>
@@ -5991,16 +5686,16 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M36">
-        <v>100</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="N36">
         <v>100</v>
       </c>
       <c r="O36">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P36">
         <v>100</v>
@@ -6009,92 +5704,92 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:19">
       <c r="A37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B37">
-        <v>100</v>
-      </c>
-      <c r="C37">
-        <v>100</v>
-      </c>
       <c r="D37">
         <v>100</v>
       </c>
       <c r="E37">
         <v>100</v>
       </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>95</v>
-      </c>
-      <c r="H37">
-        <v>100</v>
-      </c>
-      <c r="I37">
-        <v>100</v>
-      </c>
       <c r="J37">
         <v>100</v>
       </c>
       <c r="K37">
-        <v>100</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>95</v>
-      </c>
-      <c r="N37">
-        <v>100</v>
-      </c>
-      <c r="O37">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="P37">
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>100</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>95</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="B38">
+        <v>100</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
       <c r="D38">
         <v>100</v>
       </c>
       <c r="E38">
         <v>100</v>
       </c>
+      <c r="F38">
+        <v>100</v>
+      </c>
+      <c r="G38">
+        <v>75</v>
+      </c>
+      <c r="H38">
+        <v>100</v>
+      </c>
+      <c r="I38">
+        <v>45.7</v>
+      </c>
       <c r="J38">
         <v>100</v>
       </c>
       <c r="K38">
         <v>100</v>
       </c>
+      <c r="L38">
+        <v>50</v>
+      </c>
+      <c r="M38">
+        <v>83.3</v>
+      </c>
+      <c r="N38">
+        <v>100</v>
+      </c>
+      <c r="O38">
+        <v>45.7</v>
+      </c>
       <c r="P38">
         <v>100</v>
       </c>
       <c r="Q38">
         <v>100</v>
+      </c>
+      <c r="R38">
+        <v>50</v>
+      </c>
+      <c r="S38">
+        <v>83.3</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -6105,7 +5800,7 @@
         <v>100</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>95.8</v>
       </c>
       <c r="D39">
         <v>100</v>
@@ -6114,16 +5809,16 @@
         <v>100</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G39">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H39">
         <v>100</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -6132,16 +5827,16 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M39">
-        <v>75</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="N39">
         <v>100</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -6150,68 +5845,32 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S39">
-        <v>75</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:19">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B40">
-        <v>100</v>
-      </c>
-      <c r="C40">
-        <v>95.8</v>
-      </c>
       <c r="D40">
         <v>100</v>
       </c>
       <c r="E40">
         <v>100</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>100</v>
-      </c>
-      <c r="H40">
-        <v>100</v>
-      </c>
-      <c r="I40">
-        <v>95.8</v>
-      </c>
       <c r="J40">
         <v>100</v>
       </c>
       <c r="K40">
         <v>100</v>
       </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>100</v>
-      </c>
-      <c r="N40">
-        <v>100</v>
-      </c>
-      <c r="O40">
-        <v>95.8</v>
-      </c>
       <c r="P40">
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>100</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
         <v>100</v>
       </c>
     </row>
@@ -6219,23 +5878,59 @@
       <c r="A41" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="B41">
+        <v>100</v>
+      </c>
+      <c r="C41">
+        <v>100</v>
+      </c>
       <c r="D41">
         <v>100</v>
       </c>
       <c r="E41">
         <v>100</v>
       </c>
+      <c r="F41">
+        <v>100</v>
+      </c>
+      <c r="G41">
+        <v>100</v>
+      </c>
+      <c r="H41">
+        <v>100</v>
+      </c>
+      <c r="I41">
+        <v>97.8</v>
+      </c>
       <c r="J41">
         <v>100</v>
       </c>
       <c r="K41">
         <v>100</v>
       </c>
+      <c r="L41">
+        <v>50</v>
+      </c>
+      <c r="M41">
+        <v>83.3</v>
+      </c>
+      <c r="N41">
+        <v>100</v>
+      </c>
+      <c r="O41">
+        <v>97.8</v>
+      </c>
       <c r="P41">
         <v>100</v>
       </c>
       <c r="Q41">
         <v>100</v>
+      </c>
+      <c r="R41">
+        <v>50</v>
+      </c>
+      <c r="S41">
+        <v>83.3</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -6246,7 +5941,7 @@
         <v>100</v>
       </c>
       <c r="C42">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="D42">
         <v>100</v>
@@ -6255,16 +5950,16 @@
         <v>100</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H42">
         <v>100</v>
       </c>
       <c r="I42">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="J42">
         <v>100</v>
@@ -6273,16 +5968,16 @@
         <v>100</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M42">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N42">
         <v>100</v>
       </c>
       <c r="O42">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="P42">
         <v>100</v>
@@ -6291,151 +5986,92 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S42">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="43" spans="1:19">
       <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B43">
-        <v>100</v>
-      </c>
-      <c r="C43">
-        <v>95.8</v>
-      </c>
       <c r="D43">
         <v>100</v>
       </c>
       <c r="E43">
         <v>100</v>
       </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>90</v>
-      </c>
-      <c r="H43">
-        <v>100</v>
-      </c>
-      <c r="I43">
-        <v>95.8</v>
-      </c>
       <c r="J43">
         <v>100</v>
       </c>
       <c r="K43">
         <v>100</v>
       </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>90</v>
-      </c>
-      <c r="N43">
-        <v>100</v>
-      </c>
-      <c r="O43">
-        <v>95.8</v>
-      </c>
       <c r="P43">
         <v>100</v>
       </c>
       <c r="Q43">
         <v>100</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="B44">
+        <v>100</v>
+      </c>
+      <c r="C44">
+        <v>100</v>
+      </c>
       <c r="D44">
         <v>100</v>
       </c>
       <c r="E44">
         <v>100</v>
       </c>
+      <c r="F44">
+        <v>100</v>
+      </c>
+      <c r="G44">
+        <v>95</v>
+      </c>
+      <c r="H44">
+        <v>100</v>
+      </c>
+      <c r="I44">
+        <v>97.8</v>
+      </c>
       <c r="J44">
         <v>100</v>
       </c>
       <c r="K44">
         <v>100</v>
       </c>
+      <c r="L44">
+        <v>50</v>
+      </c>
+      <c r="M44">
+        <v>81</v>
+      </c>
+      <c r="N44">
+        <v>100</v>
+      </c>
+      <c r="O44">
+        <v>97.8</v>
+      </c>
       <c r="P44">
         <v>100</v>
       </c>
       <c r="Q44">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="1:19">
-      <c r="A45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45">
-        <v>100</v>
-      </c>
-      <c r="C45">
-        <v>100</v>
-      </c>
-      <c r="D45">
-        <v>100</v>
-      </c>
-      <c r="E45">
-        <v>100</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>95</v>
-      </c>
-      <c r="H45">
-        <v>100</v>
-      </c>
-      <c r="I45">
-        <v>100</v>
-      </c>
-      <c r="J45">
-        <v>100</v>
-      </c>
-      <c r="K45">
-        <v>100</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>95</v>
-      </c>
-      <c r="N45">
-        <v>100</v>
-      </c>
-      <c r="O45">
-        <v>100</v>
-      </c>
-      <c r="P45">
-        <v>100</v>
-      </c>
-      <c r="Q45">
-        <v>100</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>95</v>
+      <c r="R44">
+        <v>50</v>
+      </c>
+      <c r="S44">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -6463,83 +6099,86 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
+        <v>27</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2">
+        <v>75</v>
+      </c>
+      <c r="G2" s="2">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>37</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
-        <v>78.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="G3" s="2">
-        <v>21.6</v>
+        <v>25</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -6553,28 +6192,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>8</v>
       </c>
       <c r="F4" s="2">
-        <v>78.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="G4" s="2">
-        <v>21.6</v>
+        <v>19.5</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6585,28 +6224,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>85.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>14.3</v>
+        <v>17.1</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6617,28 +6256,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>85.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6652,25 +6291,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>91.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6686,7 +6325,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6695,762 +6334,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330061460173</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920231</v>
-      </c>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920230</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920260</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920232</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920233</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920234</v>
-      </c>
-      <c r="B8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" t="s">
-        <v>145</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920296</v>
-      </c>
-      <c r="B9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920236</v>
-      </c>
-      <c r="B10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920237</v>
-      </c>
-      <c r="B11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" t="s">
-        <v>148</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920239</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" t="s">
-        <v>149</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920240</v>
-      </c>
-      <c r="B13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920422</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920241</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920357</v>
-      </c>
-      <c r="B16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" t="s">
-        <v>153</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920243</v>
-      </c>
-      <c r="B17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" t="s">
-        <v>154</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920245</v>
-      </c>
-      <c r="B18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" t="s">
-        <v>155</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920369</v>
-      </c>
-      <c r="B19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051420317</v>
-      </c>
-      <c r="B20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920319</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" t="s">
-        <v>158</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920246</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" t="s">
-        <v>159</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920249</v>
-      </c>
-      <c r="B23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" t="s">
-        <v>160</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920414</v>
-      </c>
-      <c r="B24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" t="s">
-        <v>161</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920250</v>
-      </c>
-      <c r="B25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" t="s">
-        <v>162</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920251</v>
-      </c>
-      <c r="B26" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" t="s">
-        <v>163</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920399</v>
-      </c>
-      <c r="B27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C27" t="s">
-        <v>131</v>
-      </c>
-      <c r="D27" t="s">
-        <v>164</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920375</v>
-      </c>
-      <c r="B28" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" t="s">
-        <v>131</v>
-      </c>
-      <c r="D28" t="s">
-        <v>165</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920253</v>
-      </c>
-      <c r="B29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920235</v>
-      </c>
-      <c r="B30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" t="s">
-        <v>167</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920366</v>
-      </c>
-      <c r="B31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" t="s">
-        <v>133</v>
-      </c>
-      <c r="D31" t="s">
-        <v>168</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920368</v>
-      </c>
-      <c r="B32" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" t="s">
-        <v>169</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920254</v>
-      </c>
-      <c r="B33" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" t="s">
-        <v>170</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920257</v>
-      </c>
-      <c r="B34" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" t="s">
-        <v>134</v>
-      </c>
-      <c r="D34" t="s">
-        <v>171</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920256</v>
-      </c>
-      <c r="B35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35" t="s">
-        <v>135</v>
-      </c>
-      <c r="D35" t="s">
-        <v>172</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920401</v>
-      </c>
-      <c r="B36" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" t="s">
-        <v>173</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920259</v>
-      </c>
-      <c r="B37" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" t="s">
-        <v>137</v>
-      </c>
-      <c r="D37" t="s">
-        <v>174</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920176</v>
-      </c>
-      <c r="B38" t="s">
-        <v>111</v>
-      </c>
-      <c r="C38" t="s">
-        <v>138</v>
-      </c>
-      <c r="D38" t="s">
-        <v>175</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -7460,7 +6359,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7469,22 +6368,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -7492,22 +6391,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920237</v>
+        <v>22330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7515,25 +6414,25 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920237</v>
+        <v>22330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>66</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -7541,22 +6440,22 @@
         <v>22330051920240</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7564,19 +6463,19 @@
         <v>22330051920240</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7584,19 +6483,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920369</v>
+        <v>21330051920105</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>67</v>
@@ -7607,68 +6506,68 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920369</v>
+        <v>21330051920105</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051420317</v>
+        <v>22330051920237</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051420317</v>
+        <v>22330051920357</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7676,19 +6575,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920105</v>
+        <v>22330051920369</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>69</v>
@@ -7699,22 +6598,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920105</v>
+        <v>22330051920366</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7725,19 +6624,19 @@
         <v>22330051920256</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7745,646 +6644,25 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920256</v>
+        <v>22330051920259</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920401</v>
-      </c>
-      <c r="B14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D14" t="s">
-        <v>173</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920401</v>
-      </c>
-      <c r="B15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D15" t="s">
-        <v>173</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920259</v>
-      </c>
-      <c r="B16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" t="s">
-        <v>174</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920259</v>
-      </c>
-      <c r="B17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" t="s">
-        <v>137</v>
-      </c>
-      <c r="D17" t="s">
-        <v>174</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330061460173</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920231</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920230</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>66</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920260</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920232</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920233</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920234</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920241</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>152</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920357</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" t="s">
-        <v>153</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920243</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" t="s">
-        <v>154</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920245</v>
-      </c>
-      <c r="B28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" t="s">
-        <v>155</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920319</v>
-      </c>
-      <c r="B29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" t="s">
-        <v>158</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920246</v>
-      </c>
-      <c r="B30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" t="s">
-        <v>159</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920249</v>
-      </c>
-      <c r="B31" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" t="s">
-        <v>128</v>
-      </c>
-      <c r="D31" t="s">
-        <v>160</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920414</v>
-      </c>
-      <c r="B32" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" t="s">
-        <v>161</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920250</v>
-      </c>
-      <c r="B33" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" t="s">
-        <v>162</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>22330051920251</v>
-      </c>
-      <c r="B34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" t="s">
-        <v>163</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>22330051920375</v>
-      </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" t="s">
-        <v>131</v>
-      </c>
-      <c r="D35" t="s">
-        <v>165</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920235</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" t="s">
-        <v>132</v>
-      </c>
-      <c r="D36" t="s">
-        <v>167</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920366</v>
-      </c>
-      <c r="B37" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" t="s">
-        <v>168</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>22330051920254</v>
-      </c>
-      <c r="B38" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" t="s">
-        <v>105</v>
-      </c>
-      <c r="D38" t="s">
-        <v>170</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>66</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>22330051920257</v>
-      </c>
-      <c r="B39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" t="s">
-        <v>134</v>
-      </c>
-      <c r="D39" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>66</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>22330051920176</v>
-      </c>
-      <c r="B40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" t="s">
-        <v>138</v>
-      </c>
-      <c r="D40" t="s">
-        <v>175</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>66</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3ALCV - Estadisticos 20231.xlsx
+++ b/grupos/3ALCV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="105">
   <si>
     <t>Materia</t>
   </si>
@@ -215,6 +215,9 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
@@ -227,9 +230,6 @@
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -245,15 +245,15 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>SOLANO</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>ESCOBAR</t>
   </si>
   <si>
@@ -272,7 +272,7 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>ZAVALA</t>
   </si>
   <si>
     <t>MARQUEZ</t>
@@ -281,6 +281,9 @@
     <t>MENA</t>
   </si>
   <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -299,7 +302,7 @@
     <t>TZOMPAXTLE</t>
   </si>
   <si>
-    <t>KEVIN ALEXIS</t>
+    <t>DELGADO</t>
   </si>
   <si>
     <t>AMALIA PAULINA</t>
@@ -308,6 +311,9 @@
     <t>ANGELES</t>
   </si>
   <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
     <t>LUZ ALONDRA</t>
   </si>
   <si>
@@ -324,6 +330,9 @@
   </si>
   <si>
     <t>BRENDA JANELY</t>
+  </si>
+  <si>
+    <t>AXEL GAEL</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -1187,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1228,7 +1237,7 @@
         <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1264,7 +1273,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1305,7 +1314,7 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>9</v>
@@ -1341,7 +1350,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1382,7 +1391,7 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1536,7 +1545,7 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1572,7 +1581,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1690,7 +1699,7 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1726,7 +1735,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1844,7 +1853,7 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -2229,7 +2238,7 @@
         <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2383,7 +2392,7 @@
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2489,7 +2498,7 @@
         <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>6</v>
@@ -2525,7 +2534,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2566,7 +2575,7 @@
         <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>7</v>
@@ -2602,7 +2611,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2643,7 +2652,7 @@
         <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>8</v>
@@ -2679,7 +2688,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2720,7 +2729,7 @@
         <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -2797,7 +2806,7 @@
         <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>5</v>
@@ -2833,7 +2842,7 @@
         <v>5</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -2874,7 +2883,7 @@
         <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>8</v>
@@ -2910,7 +2919,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -2980,7 +2989,7 @@
         <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>5</v>
@@ -3057,7 +3066,7 @@
         <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>5</v>
@@ -3093,7 +3102,7 @@
         <v>6</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3134,7 +3143,7 @@
         <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3170,7 +3179,7 @@
         <v>5</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>9</v>
@@ -3211,7 +3220,7 @@
         <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
         <v>7</v>
@@ -3317,7 +3326,7 @@
         <v>7</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
         <v>6</v>
@@ -3353,7 +3362,7 @@
         <v>8</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>6</v>
@@ -3394,7 +3403,7 @@
         <v>7</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>7</v>
@@ -3500,7 +3509,7 @@
         <v>7</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M41">
         <v>5</v>
@@ -3577,7 +3586,7 @@
         <v>6</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M42">
         <v>5</v>
@@ -3613,7 +3622,7 @@
         <v>6</v>
       </c>
       <c r="X42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y42">
         <v>6</v>
@@ -3683,7 +3692,7 @@
         <v>7</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M44">
         <v>5</v>
@@ -3719,7 +3728,7 @@
         <v>7</v>
       </c>
       <c r="X44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y44">
         <v>6</v>
@@ -4106,7 +4115,7 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>95.2</v>
@@ -4124,7 +4133,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S8">
         <v>95.2</v>
@@ -4165,7 +4174,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -4183,7 +4192,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4224,7 +4233,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>92.90000000000001</v>
@@ -4242,7 +4251,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S10">
         <v>92.90000000000001</v>
@@ -4283,7 +4292,7 @@
         <v>20</v>
       </c>
       <c r="L11">
-        <v>44.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M11">
         <v>73.8</v>
@@ -4301,7 +4310,7 @@
         <v>20</v>
       </c>
       <c r="R11">
-        <v>44.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S11">
         <v>73.8</v>
@@ -4401,7 +4410,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>76.2</v>
@@ -4419,7 +4428,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S13">
         <v>76.2</v>
@@ -4519,7 +4528,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>71.40000000000001</v>
@@ -4537,7 +4546,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S15">
         <v>71.40000000000001</v>
@@ -4637,7 +4646,7 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>44.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M17">
         <v>83.3</v>
@@ -4655,7 +4664,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>44.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S17">
         <v>83.3</v>
@@ -4932,7 +4941,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>44.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M22">
         <v>88.09999999999999</v>
@@ -4950,7 +4959,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>44.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S22">
         <v>88.09999999999999</v>
@@ -5050,7 +5059,7 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>44.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M24">
         <v>71.40000000000001</v>
@@ -5068,7 +5077,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>44.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S24">
         <v>71.40000000000001</v>
@@ -5132,7 +5141,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M26">
         <v>78.59999999999999</v>
@@ -5150,7 +5159,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S26">
         <v>78.59999999999999</v>
@@ -5191,7 +5200,7 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>76.2</v>
@@ -5209,7 +5218,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S27">
         <v>76.2</v>
@@ -5250,7 +5259,7 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>92.90000000000001</v>
@@ -5268,7 +5277,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S28">
         <v>92.90000000000001</v>
@@ -5309,7 +5318,7 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>95.2</v>
@@ -5327,7 +5336,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S29">
         <v>95.2</v>
@@ -5427,7 +5436,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M31">
         <v>95.2</v>
@@ -5445,7 +5454,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S31">
         <v>95.2</v>
@@ -5509,7 +5518,7 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>44.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M33">
         <v>88.09999999999999</v>
@@ -5527,7 +5536,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>44.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S33">
         <v>88.09999999999999</v>
@@ -5568,7 +5577,7 @@
         <v>85.7</v>
       </c>
       <c r="L34">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M34">
         <v>83.3</v>
@@ -5586,7 +5595,7 @@
         <v>85.7</v>
       </c>
       <c r="R34">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S34">
         <v>83.3</v>
@@ -5627,7 +5636,7 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M35">
         <v>95.2</v>
@@ -5645,7 +5654,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S35">
         <v>95.2</v>
@@ -5686,7 +5695,7 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M36">
         <v>88.09999999999999</v>
@@ -5704,7 +5713,7 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S36">
         <v>88.09999999999999</v>
@@ -5768,7 +5777,7 @@
         <v>100</v>
       </c>
       <c r="L38">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M38">
         <v>83.3</v>
@@ -5786,7 +5795,7 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S38">
         <v>83.3</v>
@@ -5827,7 +5836,7 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M39">
         <v>88.09999999999999</v>
@@ -5845,7 +5854,7 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S39">
         <v>88.09999999999999</v>
@@ -5909,7 +5918,7 @@
         <v>100</v>
       </c>
       <c r="L41">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M41">
         <v>83.3</v>
@@ -5927,7 +5936,7 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S41">
         <v>83.3</v>
@@ -5968,7 +5977,7 @@
         <v>100</v>
       </c>
       <c r="L42">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M42">
         <v>83.3</v>
@@ -5986,7 +5995,7 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S42">
         <v>83.3</v>
@@ -6050,7 +6059,7 @@
         <v>100</v>
       </c>
       <c r="L44">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M44">
         <v>81</v>
@@ -6068,7 +6077,7 @@
         <v>100</v>
       </c>
       <c r="R44">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S44">
         <v>81</v>
@@ -6128,7 +6137,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -6137,19 +6146,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>75</v>
+        <v>72.2</v>
       </c>
       <c r="G2" s="2">
-        <v>25</v>
+        <v>27.8</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6160,7 +6169,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -6181,7 +6190,7 @@
         <v>25</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6192,28 +6201,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>80.5</v>
+        <v>75</v>
       </c>
       <c r="G4" s="2">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6224,7 +6233,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -6233,19 +6242,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2">
-        <v>82.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="G5" s="2">
-        <v>17.1</v>
+        <v>19.5</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6256,28 +6265,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
       </c>
       <c r="C6">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>86.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>13.9</v>
+        <v>17.1</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6391,19 +6400,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920236</v>
+        <v>22330051920240</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>65</v>
@@ -6414,22 +6423,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920236</v>
+        <v>22330051920240</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6437,22 +6446,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920240</v>
+        <v>21330051920105</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6460,22 +6469,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920240</v>
+        <v>21330051920105</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6483,22 +6492,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920105</v>
+        <v>22330051920233</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6506,22 +6515,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920105</v>
+        <v>22330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6529,22 +6538,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920237</v>
+        <v>22330051920357</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6552,22 +6561,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920357</v>
+        <v>22330051920369</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6575,22 +6584,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920369</v>
+        <v>22330051920366</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6598,19 +6607,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920366</v>
+        <v>22330051920256</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>66</v>
@@ -6621,22 +6630,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920256</v>
+        <v>22330051920259</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6644,19 +6653,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920259</v>
+        <v>22330051920176</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>65</v>

--- a/grupos/3ALCV - Estadisticos 20231.xlsx
+++ b/grupos/3ALCV - Estadisticos 20231.xlsx
@@ -1009,7 +1009,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1045,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1163,7 +1163,7 @@
         <v>8</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1199,7 +1199,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -3146,7 +3146,7 @@
         <v>5</v>
       </c>
       <c r="M35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3182,7 +3182,7 @@
         <v>6</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3223,7 +3223,7 @@
         <v>9</v>
       </c>
       <c r="M36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3259,7 +3259,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3329,7 +3329,7 @@
         <v>7</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3365,7 +3365,7 @@
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -6222,7 +6222,7 @@
         <v>25</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>

--- a/grupos/3ALCV - Estadisticos 20231.xlsx
+++ b/grupos/3ALCV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="90">
   <si>
     <t>Materia</t>
   </si>
@@ -215,12 +215,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
@@ -245,7 +245,7 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>DECTOR</t>
   </si>
   <si>
     <t>SOLANO</t>
@@ -254,28 +254,13 @@
     <t>BONILLA</t>
   </si>
   <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>TEPOLE</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZAVALA</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>MENA</t>
@@ -284,28 +269,13 @@
     <t>IBAÑEZ</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>TETLACTLE</t>
   </si>
   <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
+    <t>KEVIN ALEXIS</t>
   </si>
   <si>
     <t>ANGELES</t>
@@ -314,25 +284,10 @@
     <t>FERNANDA MARGARITA</t>
   </si>
   <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
     <t>AILYN</t>
   </si>
   <si>
     <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>BRENDA JANELY</t>
-  </si>
-  <si>
-    <t>AXEL GAEL</t>
   </si>
 </sst>
 </file>
@@ -858,28 +813,28 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>8</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -935,40 +890,40 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1012,22 +967,22 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1039,10 +994,10 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1089,22 +1044,22 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1119,7 +1074,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1166,22 +1121,22 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1243,28 +1198,28 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>7</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1276,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1320,22 +1275,22 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1350,10 +1305,10 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1397,22 +1352,22 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1474,22 +1429,22 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1551,22 +1506,22 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1581,7 +1536,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1628,28 +1583,28 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>8</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1658,10 +1613,10 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1705,22 +1660,22 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1782,22 +1737,22 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -1806,16 +1761,16 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1859,40 +1814,40 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>8</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1936,28 +1891,28 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2013,37 +1968,37 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>6</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2090,22 +2045,22 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2120,7 +2075,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2167,25 +2122,25 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2197,7 +2152,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2244,25 +2199,25 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2274,10 +2229,10 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2321,28 +2276,28 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>10</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2398,28 +2353,28 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2451,10 +2406,10 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>8</v>
@@ -2504,22 +2459,22 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2534,7 +2489,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2581,22 +2536,22 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2614,7 +2569,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2658,22 +2613,22 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2735,25 +2690,25 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -2765,7 +2720,7 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -2812,25 +2767,25 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -2889,22 +2844,22 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -2922,7 +2877,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2942,10 +2897,10 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>8</v>
@@ -2995,40 +2950,40 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3072,28 +3027,28 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>7</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -3105,7 +3060,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3149,40 +3104,40 @@
         <v>7</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>6</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3226,22 +3181,22 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3253,10 +3208,10 @@
         <v>9</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>10</v>
@@ -3279,10 +3234,10 @@
         <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V37">
         <v>5</v>
@@ -3332,25 +3287,25 @@
         <v>7</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U38">
         <v>5</v>
@@ -3362,10 +3317,10 @@
         <v>8</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y38">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3409,22 +3364,22 @@
         <v>7</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
         <v>8</v>
@@ -3439,7 +3394,7 @@
         <v>7</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>8</v>
@@ -3462,10 +3417,10 @@
         <v>8</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V40">
         <v>8</v>
@@ -3515,22 +3470,22 @@
         <v>5</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T41">
         <v>7</v>
@@ -3539,16 +3494,16 @@
         <v>6</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X41">
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3592,34 +3547,34 @@
         <v>5</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X42">
         <v>7</v>
@@ -3645,10 +3600,10 @@
         <v>7</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V43">
         <v>7</v>
@@ -3698,22 +3653,22 @@
         <v>5</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T44">
         <v>7</v>
@@ -3728,7 +3683,7 @@
         <v>7</v>
       </c>
       <c r="X44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y44">
         <v>6</v>
@@ -3888,7 +3843,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -3897,10 +3852,10 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S4">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3959,7 +3914,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>88.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4015,10 +3970,10 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S6">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4065,7 +4020,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -4074,10 +4029,10 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S7">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4136,7 +4091,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>95.2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4183,7 +4138,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>97.8</v>
+        <v>95.5</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -4254,7 +4209,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>92.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4298,22 +4253,22 @@
         <v>73.8</v>
       </c>
       <c r="N11">
+        <v>31.3</v>
+      </c>
+      <c r="O11">
+        <v>4.5</v>
+      </c>
+      <c r="P11">
+        <v>12.5</v>
+      </c>
+      <c r="Q11">
         <v>50</v>
-      </c>
-      <c r="O11">
-        <v>6.5</v>
-      </c>
-      <c r="P11">
-        <v>20</v>
-      </c>
-      <c r="Q11">
-        <v>20</v>
       </c>
       <c r="R11">
         <v>94.40000000000001</v>
       </c>
       <c r="S11">
-        <v>73.8</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4372,7 +4327,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>95.2</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4419,7 +4374,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>95.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4428,10 +4383,10 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S13">
-        <v>76.2</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4478,7 +4433,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4487,10 +4442,10 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S14">
-        <v>81</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4534,13 +4489,13 @@
         <v>71.40000000000001</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>70.3</v>
       </c>
       <c r="O15">
-        <v>95.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4549,7 +4504,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>71.40000000000001</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4596,7 +4551,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4605,10 +4560,10 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="S16">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4655,7 +4610,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4667,7 +4622,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="S17">
-        <v>83.3</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4714,7 +4669,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>97.8</v>
+        <v>95.5</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -4726,7 +4681,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>92.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4785,7 +4740,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="S19">
-        <v>95.2</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4844,7 +4799,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>95.2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4903,7 +4858,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>95.2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4950,7 +4905,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4962,7 +4917,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="S22">
-        <v>88.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5021,7 +4976,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>90.5</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5068,7 +5023,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>95.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5080,7 +5035,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="S24">
-        <v>71.40000000000001</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5150,7 +5105,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -5162,7 +5117,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>78.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5218,10 +5173,10 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S27">
-        <v>76.2</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5277,10 +5232,10 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S28">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5327,7 +5282,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -5339,7 +5294,7 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>95.2</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5383,22 +5338,22 @@
         <v>73.8</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="O30">
-        <v>50</v>
+        <v>34.8</v>
       </c>
       <c r="P30">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="Q30">
-        <v>85.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="R30">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="S30">
-        <v>73.8</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5445,7 +5400,7 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -5457,7 +5412,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>95.2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5527,7 +5482,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5536,10 +5491,10 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="S33">
-        <v>88.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5586,19 +5541,19 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>93.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P34">
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>85.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S34">
-        <v>83.3</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5645,7 +5600,7 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -5657,7 +5612,7 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>95.2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5704,7 +5659,7 @@
         <v>100</v>
       </c>
       <c r="O36">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="P36">
         <v>100</v>
@@ -5716,7 +5671,7 @@
         <v>100</v>
       </c>
       <c r="S36">
-        <v>88.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5736,10 +5691,10 @@
         <v>85.7</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="Q37">
-        <v>85.7</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5786,7 +5741,7 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>45.7</v>
+        <v>62.1</v>
       </c>
       <c r="P38">
         <v>100</v>
@@ -5798,7 +5753,7 @@
         <v>100</v>
       </c>
       <c r="S38">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5845,7 +5800,7 @@
         <v>100</v>
       </c>
       <c r="O39">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -5854,10 +5809,10 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S39">
-        <v>88.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -5927,7 +5882,7 @@
         <v>100</v>
       </c>
       <c r="O41">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="P41">
         <v>100</v>
@@ -5936,10 +5891,10 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S41">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -5986,7 +5941,7 @@
         <v>100</v>
       </c>
       <c r="O42">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="P42">
         <v>100</v>
@@ -5995,10 +5950,10 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S42">
-        <v>83.3</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6068,7 +6023,7 @@
         <v>100</v>
       </c>
       <c r="O44">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="P44">
         <v>100</v>
@@ -6077,10 +6032,10 @@
         <v>100</v>
       </c>
       <c r="R44">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S44">
-        <v>81</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6137,7 +6092,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -6146,19 +6101,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>72.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>27.8</v>
+        <v>19.4</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6169,7 +6124,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -6178,19 +6133,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>75</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>25</v>
+        <v>13.9</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6210,16 +6165,16 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>75</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>25</v>
+        <v>13.9</v>
       </c>
       <c r="H4">
         <v>7.1</v>
@@ -6242,19 +6197,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>80.5</v>
+        <v>90.2</v>
       </c>
       <c r="G5" s="2">
-        <v>19.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6274,16 +6229,16 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>82.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="G6" s="2">
-        <v>17.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H6">
         <v>7.2</v>
@@ -6306,16 +6261,16 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>88.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="G7" s="2">
-        <v>11.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H7">
         <v>7.8</v>
@@ -6368,7 +6323,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6400,19 +6355,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920240</v>
+        <v>22330051920236</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" t="s">
         <v>85</v>
       </c>
-      <c r="D2" t="s">
-        <v>95</v>
-      </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>65</v>
@@ -6423,16 +6378,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920240</v>
+        <v>22330051920236</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
         <v>85</v>
-      </c>
-      <c r="D3" t="s">
-        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6452,10 +6407,10 @@
         <v>76</v>
       </c>
       <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
         <v>86</v>
-      </c>
-      <c r="D4" t="s">
-        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -6475,10 +6430,10 @@
         <v>76</v>
       </c>
       <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" t="s">
         <v>86</v>
-      </c>
-      <c r="D5" t="s">
-        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -6498,16 +6453,16 @@
         <v>77</v>
       </c>
       <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
         <v>87</v>
       </c>
-      <c r="D6" t="s">
-        <v>97</v>
-      </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6515,22 +6470,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920237</v>
+        <v>22330051920366</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" t="s">
         <v>88</v>
       </c>
-      <c r="D7" t="s">
-        <v>98</v>
-      </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6538,139 +6493,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920357</v>
+        <v>22330051920256</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" t="s">
         <v>89</v>
       </c>
-      <c r="D8" t="s">
-        <v>99</v>
-      </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920369</v>
-      </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920366</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920256</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920259</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920176</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ALCV - Estadisticos 20231.xlsx
+++ b/grupos/3ALCV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="90">
   <si>
     <t>Materia</t>
   </si>
@@ -248,6 +248,9 @@
     <t>DECTOR</t>
   </si>
   <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
@@ -257,12 +260,12 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>MENA</t>
   </si>
   <si>
@@ -272,12 +275,12 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
     <t>KEVIN ALEXIS</t>
   </si>
   <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
     <t>ANGELES</t>
   </si>
   <si>
@@ -285,9 +288,6 @@
   </si>
   <si>
     <t>AILYN</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1210,7 @@
         <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>5</v>
@@ -1364,7 +1364,7 @@
         <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>5</v>
@@ -1672,7 +1672,7 @@
         <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>5</v>
@@ -2365,7 +2365,7 @@
         <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
         <v>8</v>
@@ -2386,7 +2386,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2779,7 +2779,7 @@
         <v>5</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>5</v>
@@ -3116,7 +3116,7 @@
         <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S35">
         <v>5</v>
@@ -3308,7 +3308,7 @@
         <v>8</v>
       </c>
       <c r="U38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -5035,7 +5035,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="S24">
-        <v>77.3</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5705,7 +5705,7 @@
         <v>100</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>95.8</v>
       </c>
       <c r="D38">
         <v>100</v>
@@ -5723,7 +5723,7 @@
         <v>100</v>
       </c>
       <c r="I38">
-        <v>45.7</v>
+        <v>95.7</v>
       </c>
       <c r="J38">
         <v>100</v>
@@ -5741,7 +5741,7 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>62.1</v>
+        <v>97</v>
       </c>
       <c r="P38">
         <v>100</v>
@@ -6101,16 +6101,16 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>80.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="G2" s="2">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="H2">
         <v>6.9</v>
@@ -6165,16 +6165,16 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>86.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="H4">
         <v>7.1</v>
@@ -6323,7 +6323,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6401,7 +6401,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920105</v>
+        <v>21330051420317</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
@@ -6413,10 +6413,10 @@
         <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6424,7 +6424,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920105</v>
+        <v>21330051420317</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
@@ -6436,10 +6436,10 @@
         <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920233</v>
+        <v>21330051920105</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
@@ -6459,10 +6459,10 @@
         <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6470,22 +6470,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920366</v>
+        <v>21330051920105</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6493,24 +6493,47 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920256</v>
+        <v>22330051920233</v>
       </c>
       <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920366</v>
+      </c>
+      <c r="B9" t="s">
         <v>79</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>84</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>89</v>
       </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
         <v>65</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ALCV - Estadisticos 20231.xlsx
+++ b/grupos/3ALCV - Estadisticos 20231.xlsx
@@ -831,22 +831,22 @@
         <v>7</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -908,22 +908,22 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -988,19 +988,19 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1062,22 +1062,22 @@
         <v>8</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1142,19 +1142,19 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1216,22 +1216,22 @@
         <v>5</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1293,22 +1293,22 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1450,19 +1450,19 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1524,19 +1524,19 @@
         <v>5</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>5</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1601,22 +1601,22 @@
         <v>5</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1755,22 +1755,22 @@
         <v>8</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1832,22 +1832,22 @@
         <v>8</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1909,22 +1909,22 @@
         <v>8</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1986,22 +1986,22 @@
         <v>6</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2066,19 +2066,19 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2140,19 +2140,19 @@
         <v>10</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2217,22 +2217,22 @@
         <v>5</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2297,19 +2297,19 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2371,22 +2371,22 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>5</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2412,10 +2412,10 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2477,22 +2477,22 @@
         <v>6</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2557,19 +2557,19 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2631,22 +2631,22 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2708,22 +2708,22 @@
         <v>9</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2862,22 +2862,22 @@
         <v>7</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2903,10 +2903,10 @@
         <v>8</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2968,22 +2968,22 @@
         <v>8</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3045,22 +3045,22 @@
         <v>7</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U34">
         <v>5</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3122,22 +3122,22 @@
         <v>5</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3202,16 +3202,16 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
         <v>10</v>
@@ -3305,22 +3305,22 @@
         <v>6</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3382,22 +3382,22 @@
         <v>8</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3423,10 +3423,10 @@
         <v>8</v>
       </c>
       <c r="V40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3488,22 +3488,22 @@
         <v>5</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y41">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3565,22 +3565,22 @@
         <v>6</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y42">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3606,10 +3606,10 @@
         <v>7</v>
       </c>
       <c r="V43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3671,22 +3671,22 @@
         <v>6</v>
       </c>
       <c r="T44">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U44">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V44">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W44">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X44">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y44">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -6113,7 +6113,7 @@
         <v>16.7</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6145,7 +6145,7 @@
         <v>13.9</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>11.1</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6209,7 +6209,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6273,7 +6273,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3ALCV - Estadisticos 20231.xlsx
+++ b/grupos/3ALCV - Estadisticos 20231.xlsx
@@ -831,22 +831,22 @@
         <v>7</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -908,22 +908,22 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -988,19 +988,19 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1062,22 +1062,22 @@
         <v>8</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1142,19 +1142,19 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1216,22 +1216,22 @@
         <v>5</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1293,22 +1293,22 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1450,19 +1450,19 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1524,19 +1524,19 @@
         <v>5</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>5</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1601,22 +1601,22 @@
         <v>5</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1755,22 +1755,22 @@
         <v>8</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1832,22 +1832,22 @@
         <v>8</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1909,22 +1909,22 @@
         <v>8</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1986,22 +1986,22 @@
         <v>6</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2066,19 +2066,19 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2140,19 +2140,19 @@
         <v>10</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2217,22 +2217,22 @@
         <v>5</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2279,7 +2279,7 @@
         <v>10</v>
       </c>
       <c r="O23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>9</v>
@@ -2300,16 +2300,16 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2371,22 +2371,22 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>5</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2412,10 +2412,10 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2477,22 +2477,22 @@
         <v>6</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2557,19 +2557,19 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2631,22 +2631,22 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2708,22 +2708,22 @@
         <v>9</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2862,22 +2862,22 @@
         <v>7</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2903,10 +2903,10 @@
         <v>8</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2968,22 +2968,22 @@
         <v>8</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3045,22 +3045,22 @@
         <v>7</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>5</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3122,22 +3122,22 @@
         <v>5</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3202,16 +3202,16 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>10</v>
@@ -3305,22 +3305,22 @@
         <v>6</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y38">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3382,22 +3382,22 @@
         <v>8</v>
       </c>
       <c r="T39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y39">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3423,10 +3423,10 @@
         <v>8</v>
       </c>
       <c r="V40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W40">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3488,22 +3488,22 @@
         <v>5</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y41">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3565,22 +3565,22 @@
         <v>6</v>
       </c>
       <c r="T42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y42">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3606,10 +3606,10 @@
         <v>7</v>
       </c>
       <c r="V43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W43">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3671,22 +3671,22 @@
         <v>6</v>
       </c>
       <c r="T44">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W44">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y44">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6113,7 +6113,7 @@
         <v>16.7</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6145,7 +6145,7 @@
         <v>13.9</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>11.1</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6209,7 +6209,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6273,7 +6273,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
